--- a/response.xlsx
+++ b/response.xlsx
@@ -6,15 +6,18 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Response" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Username</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
   <si>
     <t>Response</t>
@@ -65,7 +68,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -75,15 +78,18 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
         <v>200.0</v>
       </c>
-      <c r="D2" t="b">
+      <c r="C2" t="b">
         <v>1</v>
       </c>
     </row>
